--- a/outputs/RKO/parameters/MK-2206_parameters.xlsx
+++ b/outputs/RKO/parameters/MK-2206_parameters.xlsx
@@ -428,7 +428,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3999999999999995</v>
+        <v>0.6004433731970973</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.009071694127035</v>
+        <v>0.9999087762055086</v>
       </c>
     </row>
     <row r="4">
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.022418628579314</v>
+        <v>0.9859114742644216</v>
       </c>
     </row>
     <row r="5">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5036324166532663</v>
+        <v>0.6736933893521244</v>
       </c>
     </row>
   </sheetData>
